--- a/Data/SM/SM_Quizzes.xlsx
+++ b/Data/SM/SM_Quizzes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\Semester 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\SM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E96CFB-9219-494D-B18F-D87ABF76B5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E585759C-18DA-4E76-935E-87CDFF31D56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="13" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1118">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -3453,6 +3453,12 @@
   </si>
   <si>
     <t>37</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -3546,14 +3552,15 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{03F22068-AF22-44BD-92B9-B1C339EE0FF9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3561,14 +3568,15 @@
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_10" connectionId="2" xr16:uid="{4F470084-FD73-42D2-A4F6-F8C4DC3D2C82}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3576,14 +3584,15 @@
 
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_11" connectionId="3" xr16:uid="{BAA96576-5879-45E1-A591-FC7B2E4F22A2}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3591,14 +3600,15 @@
 
 <file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_12" connectionId="4" xr16:uid="{AA278392-39FA-471B-B795-3EEB7A7B3AD0}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3606,14 +3616,15 @@
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="5" xr16:uid="{FBE7214E-193F-4E40-89C3-A2D980000A3C}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3621,14 +3632,15 @@
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="6" xr16:uid="{25E51CF9-8C8D-4AAA-864C-3DF1215093A7}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3636,14 +3648,15 @@
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="7" xr16:uid="{1D6A8D9C-0236-43D1-AC33-50F3E395CDF5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3651,14 +3664,15 @@
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_5" connectionId="8" xr16:uid="{EE764CFE-C1F3-478E-9189-546A2B3C47B3}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3666,14 +3680,15 @@
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_6" connectionId="9" xr16:uid="{5589AEDA-DAD0-4E01-9F21-8F2F7CDEC133}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3681,14 +3696,15 @@
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_7" connectionId="10" xr16:uid="{C2BBE573-063A-4035-AE8E-2AC036924C67}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3696,14 +3712,15 @@
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_8" connectionId="11" xr16:uid="{E40C8DA1-8314-4AB4-A98B-A13B6C8980E6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3711,194 +3728,207 @@
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_9" connectionId="12" xr16:uid="{50F4801D-51C6-43FB-A157-90D7B0F7E313}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{616BAF0A-2E04-47A3-93C1-6ACE477FF147}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{616BAF0A-2E04-47A3-93C1-6ACE477FF147}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0F60ECBD-2372-404A-A644-7C5AE4520C7C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{616BAF0A-2E04-47A3-93C1-6ACE477FF147}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{616BAF0A-2E04-47A3-93C1-6ACE477FF147}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{0F60ECBD-2372-404A-A644-7C5AE4520C7C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{23FA2E14-9E4E-4904-9E58-9863C1638C49}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{5512F36D-133E-40C4-A5C3-CA8C135F24E8}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{264690ED-5C56-4D07-8305-AFD4F2E28CFB}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{583F4E97-C1D1-4586-A27F-A0778D44C349}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{95C5577F-0D5F-4F6D-8BF7-34EFB65184D6}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{DECED38C-802F-4432-9E9D-FCA22EF23C8E}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{D5B93112-B70A-4995-AE5B-95E26A6E83A3}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{D5B93112-B70A-4995-AE5B-95E26A6E83A3}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{CAA81588-CAC2-4A43-8F00-ACFF82BF6F32}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{D5B93112-B70A-4995-AE5B-95E26A6E83A3}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{D5B93112-B70A-4995-AE5B-95E26A6E83A3}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{CAA81588-CAC2-4A43-8F00-ACFF82BF6F32}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{5AA483FC-EA8A-43D3-A445-B824AD007D10}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{58298F7D-D70A-4C97-BD14-0CE20D468B53}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F49C8B6F-F1FC-4392-B8E4-6061039545DE}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{AA1610EB-4F03-4942-A857-DE8A69628923}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{95E2D807-8FFF-43CA-B225-EC98632B0C86}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{68F1C67A-9124-40F2-A969-83A67832667A}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{38F9010E-D4B1-4CBC-84B0-E38700495879}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{38F9010E-D4B1-4CBC-84B0-E38700495879}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{57810CCF-F261-4B4F-8575-86846ACE15C0}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{38F9010E-D4B1-4CBC-84B0-E38700495879}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{38F9010E-D4B1-4CBC-84B0-E38700495879}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{57810CCF-F261-4B4F-8575-86846ACE15C0}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{390EC952-F57A-42A9-8B3A-5DF251D894F7}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{4FB6388B-8877-47DA-B462-3349FA34308E}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{C26905D3-6D46-4C4D-947B-38978A207B06}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{32FA29F2-27C8-4F00-B1E6-89FE4334FB0B}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{AB1F6B86-9EF8-4F2A-BD59-BAFF40859569}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{B471A1BE-2072-4438-8D0E-D7CBEBEEAD7C}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{03A7799B-2C2D-4C43-A52B-9DDA100933A5}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{03A7799B-2C2D-4C43-A52B-9DDA100933A5}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{FB7847C5-7D16-46CB-ACD8-40B6083E87FC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{03A7799B-2C2D-4C43-A52B-9DDA100933A5}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{03A7799B-2C2D-4C43-A52B-9DDA100933A5}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{FB7847C5-7D16-46CB-ACD8-40B6083E87FC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{1FA493B3-8B42-4199-B9B9-C91C48C02F83}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{8BBF4B8D-797A-47B7-87B0-34B2EA4F2FD5}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{93AC85DC-2AA2-447A-BE7C-EA31D315E5ED}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{405D3E12-FCB0-4CA1-9293-905B56B976C4}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{4A90A628-B3E6-41C5-B7D4-CA1921D7C309}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{2D847ACB-5E14-4742-8922-197508EA7B86}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{4D2695C5-2EE3-4002-AAE0-F938C2652189}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{4D2695C5-2EE3-4002-AAE0-F938C2652189}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7D3FFAD6-C5DF-4540-906B-F0FBA18C53C1}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{4D2695C5-2EE3-4002-AAE0-F938C2652189}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{4D2695C5-2EE3-4002-AAE0-F938C2652189}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{7D3FFAD6-C5DF-4540-906B-F0FBA18C53C1}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{70606C8D-BAF2-40BF-A970-47FF70E3AC3F}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F79CB9DB-3D75-46E1-9061-30146161DAB0}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{6F283A8C-B5CC-47D9-8684-3C7498CDAD9C}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{BD212E84-998F-4039-8CEB-3D6AED2E880B}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{61EB3229-A0EE-4EE7-9090-C81D6C800FD2}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{58EF6E11-E960-492B-8B1F-8C98B860CAEE}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{1C0DE1A5-65DE-41BA-A7BF-9797F86BF769}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{1C0DE1A5-65DE-41BA-A7BF-9797F86BF769}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D0B0DEED-495E-4483-B30E-E04869DF0981}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{1C0DE1A5-65DE-41BA-A7BF-9797F86BF769}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{1C0DE1A5-65DE-41BA-A7BF-9797F86BF769}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{D0B0DEED-495E-4483-B30E-E04869DF0981}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{31F850B3-F862-4B23-B69C-FE5BCDCE032E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{9128C121-2749-4D72-9C24-822523F6D054}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{762F8B41-7D34-4F5B-B305-46F269CA4B2C}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{3A31561C-0001-494B-81C6-A1AA84CBC8FE}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{530EA6BF-7054-436D-93F3-36E8DD1C3BD0}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{AC4B42C3-DDD1-4399-94FA-F404ABE870C4}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{7DD252F3-53C4-4056-A873-F03054EAE9A4}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{7DD252F3-53C4-4056-A873-F03054EAE9A4}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{694671D4-908C-4BC3-8CB2-36F85EF7C48B}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{7DD252F3-53C4-4056-A873-F03054EAE9A4}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{7DD252F3-53C4-4056-A873-F03054EAE9A4}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{694671D4-908C-4BC3-8CB2-36F85EF7C48B}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{0B5454D4-7D6D-48F2-BD55-9B40E9517088}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{B9433642-3713-43F0-9F87-FE6D5240D431}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{4A68B9E7-A55A-4350-BD28-B29802272A92}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{F4626536-A5C0-44BE-9413-CF09545D9FB2}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{48A87C69-FD7B-458D-B906-EF380A4E3B24}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{2CDD8E03-C5E7-48D4-9F38-4CD3B11BA3D6}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{9F0EABB6-949C-4B2D-8C76-48B7122B0D07}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{9F0EABB6-949C-4B2D-8C76-48B7122B0D07}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C1F48CEB-B028-43E8-A461-B342AB4EB59A}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{9F0EABB6-949C-4B2D-8C76-48B7122B0D07}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{9F0EABB6-949C-4B2D-8C76-48B7122B0D07}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C1F48CEB-B028-43E8-A461-B342AB4EB59A}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{66363C3D-ABFB-4B49-A8B2-D80BA7D948F9}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F1AFDE4E-198D-4B66-9B74-949D2C819D70}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{637AE2D1-412C-4BF7-82B4-6C22770118E0}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{1715B3C5-73E8-440E-8292-74C46845A80A}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{390D671C-82A3-4D54-8E3E-3109E556A8EB}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{3A3FFCD4-8AFD-452C-9186-0717454B5067}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{AC640FB1-1D48-4F3D-8052-84816370B0C4}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{AC640FB1-1D48-4F3D-8052-84816370B0C4}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4B330221-DA7E-48E6-A0B1-38B26972FC14}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{AC640FB1-1D48-4F3D-8052-84816370B0C4}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{AC640FB1-1D48-4F3D-8052-84816370B0C4}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4B330221-DA7E-48E6-A0B1-38B26972FC14}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{BE666435-1E6F-43EF-A0B6-077FB29840AA}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{D1653803-716D-41BE-BB64-7263E3A4F9AA}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F622F406-F5F5-4098-AB34-1617BEE38C51}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{C01D1954-0FE0-48E7-A3A8-797ECBEB9003}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{B89096B0-BEB9-42B8-9612-5701621717D4}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{0D6FBFF4-925F-4E62-A433-AF543E1F5665}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{CB33852C-3001-421E-8C03-42629A89C996}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{CB33852C-3001-421E-8C03-42629A89C996}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8DE3BFF5-7119-4A33-9F6A-A4B371861655}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{CB33852C-3001-421E-8C03-42629A89C996}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{CB33852C-3001-421E-8C03-42629A89C996}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{8DE3BFF5-7119-4A33-9F6A-A4B371861655}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{90BA99B9-F362-478D-ABFA-B911B9CD3CDE}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{9413D764-53AD-4162-B6B5-4C3B3C7BD60E}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{D8245164-BA11-48CA-8129-845A84512CB0}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{C61169DB-7FDE-4A55-A97C-FCBFBDBB893F}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5665C24C-80D8-4986-9394-B43A006C7ACD}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{1E22EE9E-06C9-4999-B7E6-071C1D79DE93}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{70CE0DBE-A61F-4813-94E9-0875FFC06BE7}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{70CE0DBE-A61F-4813-94E9-0875FFC06BE7}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4F546DA0-A949-41CB-B8D6-BB64B09DEEDD}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{70CE0DBE-A61F-4813-94E9-0875FFC06BE7}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{70CE0DBE-A61F-4813-94E9-0875FFC06BE7}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4F546DA0-A949-41CB-B8D6-BB64B09DEEDD}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{72F4BEE8-5401-4E60-B7AB-D16FD6B465D4}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{9694F352-D1BC-47F3-A065-FE28F36DA700}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F900E571-28B0-4C96-8D4D-21B81D6E71BE}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{16D22F18-B5A1-4AD8-9EB8-5985051A4E5C}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{571C6CD9-4B92-46A5-8003-12CB1A741F3A}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{C81B7565-C333-4C98-B625-1C1F054EE990}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{FB6223DB-667B-4765-8493-91FFD6E0F6B9}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{FB6223DB-667B-4765-8493-91FFD6E0F6B9}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F3B46E40-2F78-4B0E-A72E-466139B5A990}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{FB6223DB-667B-4765-8493-91FFD6E0F6B9}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{FB6223DB-667B-4765-8493-91FFD6E0F6B9}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{F3B46E40-2F78-4B0E-A72E-466139B5A990}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3FAFBB22-70A9-45B2-8303-042DC9D5AA2D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E1B293B8-9903-4189-8A59-17C60E47A09F}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{0B764349-DD99-4BA6-ADAA-48BEB547914C}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{1602F9A4-A562-45A2-AFF0-4EF1524321B0}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{56FAA07A-3308-4F28-AB66-542AA1D7C11C}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{EFA4BF6F-97AB-4CBA-B4DD-05B1C38AA554}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4222,7 +4252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46E6BBF-18B3-476A-87EB-AA3893261EE6}">
   <sheetPr codeName="Sheet24"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4233,7 +4263,7 @@
     <col min="6" max="6" width="69.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -4252,8 +4282,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4272,8 +4305,11 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4292,8 +4328,11 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4312,8 +4351,11 @@
       <c r="F4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4332,8 +4374,11 @@
       <c r="F5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4352,8 +4397,11 @@
       <c r="F6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4372,8 +4420,11 @@
       <c r="F7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4392,8 +4443,11 @@
       <c r="F8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4412,8 +4466,11 @@
       <c r="F9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4432,8 +4489,11 @@
       <c r="F10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -4452,8 +4512,11 @@
       <c r="F11" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -4472,8 +4535,11 @@
       <c r="F12" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4492,8 +4558,11 @@
       <c r="F13" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -4512,8 +4581,11 @@
       <c r="F14" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -4532,8 +4604,11 @@
       <c r="F15" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -4552,8 +4627,11 @@
       <c r="F16" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -4572,8 +4650,11 @@
       <c r="F17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -4592,8 +4673,11 @@
       <c r="F18" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -4612,8 +4696,11 @@
       <c r="F19" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -4632,8 +4719,11 @@
       <c r="F20" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -4651,6 +4741,9 @@
       </c>
       <c r="F21" t="s">
         <v>114</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -4664,7 +4757,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3500B2-BCDC-481C-B76E-AF15B622015B}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4675,7 +4768,7 @@
     <col min="6" max="6" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -4694,8 +4787,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4714,8 +4810,11 @@
       <c r="F2" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4734,8 +4833,11 @@
       <c r="F3" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4754,8 +4856,11 @@
       <c r="F4" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4774,8 +4879,11 @@
       <c r="F5" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4794,8 +4902,11 @@
       <c r="F6" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4814,8 +4925,11 @@
       <c r="F7" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4834,8 +4948,11 @@
       <c r="F8" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4854,8 +4971,11 @@
       <c r="F9" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4874,8 +4994,11 @@
       <c r="F10" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -4894,8 +5017,11 @@
       <c r="F11" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -4914,8 +5040,11 @@
       <c r="F12" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4934,8 +5063,11 @@
       <c r="F13" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -4954,8 +5086,11 @@
       <c r="F14" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -4974,8 +5109,11 @@
       <c r="F15" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -4994,8 +5132,11 @@
       <c r="F16" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -5014,8 +5155,11 @@
       <c r="F17" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -5034,8 +5178,11 @@
       <c r="F18" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -5054,8 +5201,11 @@
       <c r="F19" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -5074,8 +5224,11 @@
       <c r="F20" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5093,6 +5246,9 @@
       </c>
       <c r="F21" t="s">
         <v>925</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -5106,7 +5262,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78DCFB77-A57F-4F8E-89CF-958358EC22D7}">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5117,7 +5273,7 @@
     <col min="6" max="6" width="42.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -5136,8 +5292,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5156,8 +5315,11 @@
       <c r="F2" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5176,8 +5338,11 @@
       <c r="F3" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5196,8 +5361,11 @@
       <c r="F4" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5216,8 +5384,11 @@
       <c r="F5" t="s">
         <v>942</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -5236,8 +5407,11 @@
       <c r="F6" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -5256,8 +5430,11 @@
       <c r="F7" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -5276,8 +5453,11 @@
       <c r="F8" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -5296,8 +5476,11 @@
       <c r="F9" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -5316,8 +5499,11 @@
       <c r="F10" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -5336,8 +5522,11 @@
       <c r="F11" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -5356,8 +5545,11 @@
       <c r="F12" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -5376,8 +5568,11 @@
       <c r="F13" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -5396,8 +5591,11 @@
       <c r="F14" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -5416,8 +5614,11 @@
       <c r="F15" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -5436,8 +5637,11 @@
       <c r="F16" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -5456,8 +5660,11 @@
       <c r="F17" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -5476,8 +5683,11 @@
       <c r="F18" t="s">
         <v>1109</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -5496,8 +5706,11 @@
       <c r="F19" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -5516,8 +5729,11 @@
       <c r="F20" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5535,6 +5751,9 @@
       </c>
       <c r="F21" t="s">
         <v>1014</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -5548,7 +5767,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF98ECD6-8454-484A-84DD-CD07ABA34888}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5559,7 +5778,7 @@
     <col min="6" max="6" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -5578,8 +5797,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5598,8 +5820,11 @@
       <c r="F2" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5618,8 +5843,11 @@
       <c r="F3" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5638,8 +5866,11 @@
       <c r="F4" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5658,8 +5889,11 @@
       <c r="F5" t="s">
         <v>1033</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -5678,8 +5912,11 @@
       <c r="F6" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -5698,8 +5935,11 @@
       <c r="F7" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -5718,8 +5958,11 @@
       <c r="F8" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -5738,8 +5981,11 @@
       <c r="F9" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -5758,8 +6004,11 @@
       <c r="F10" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -5778,8 +6027,11 @@
       <c r="F11" t="s">
         <v>1059</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -5798,8 +6050,11 @@
       <c r="F12" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -5818,8 +6073,11 @@
       <c r="F13" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -5838,8 +6096,11 @@
       <c r="F14" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -5858,8 +6119,11 @@
       <c r="F15" t="s">
         <v>1075</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -5878,8 +6142,11 @@
       <c r="F16" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -5898,8 +6165,11 @@
       <c r="F17" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -5918,8 +6188,11 @@
       <c r="F18" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -5938,8 +6211,11 @@
       <c r="F19" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -5958,8 +6234,11 @@
       <c r="F20" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5977,6 +6256,9 @@
       </c>
       <c r="F21" t="s">
         <v>1075</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -5990,7 +6272,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB304A9-DC45-43ED-846F-F975B2A97D0F}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6001,7 +6283,7 @@
     <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -6020,8 +6302,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6040,8 +6325,11 @@
       <c r="F2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -6060,8 +6348,11 @@
       <c r="F3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -6080,8 +6371,11 @@
       <c r="F4" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -6100,8 +6394,11 @@
       <c r="F5" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -6120,8 +6417,11 @@
       <c r="F6" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -6140,8 +6440,11 @@
       <c r="F7" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -6160,8 +6463,11 @@
       <c r="F8" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -6180,8 +6486,11 @@
       <c r="F9" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>110</v>
       </c>
@@ -6200,8 +6509,11 @@
       <c r="F10" t="s">
         <v>1111</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -6220,8 +6532,11 @@
       <c r="F11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -6240,8 +6555,11 @@
       <c r="F12" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6260,8 +6578,11 @@
       <c r="F13" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -6280,8 +6601,11 @@
       <c r="F14" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -6300,8 +6624,11 @@
       <c r="F15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -6320,8 +6647,11 @@
       <c r="F16" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -6340,8 +6670,11 @@
       <c r="F17" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -6360,8 +6693,11 @@
       <c r="F18" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -6380,8 +6716,11 @@
       <c r="F19" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -6400,8 +6739,11 @@
       <c r="F20" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -6419,6 +6761,9 @@
       </c>
       <c r="F21" t="s">
         <v>168</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -6432,7 +6777,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{935A629A-7856-4DB0-AA7B-44FDC9830D82}">
   <sheetPr codeName="Sheet22"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6443,7 +6788,7 @@
     <col min="6" max="6" width="50.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -6462,8 +6807,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6482,8 +6830,11 @@
       <c r="F2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6502,8 +6853,11 @@
       <c r="F3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6522,8 +6876,11 @@
       <c r="F4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6542,8 +6899,11 @@
       <c r="F5" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6562,8 +6922,11 @@
       <c r="F6" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6582,8 +6945,11 @@
       <c r="F7" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6602,8 +6968,11 @@
       <c r="F8" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6622,8 +6991,11 @@
       <c r="F9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6642,8 +7014,11 @@
       <c r="F10" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -6662,8 +7037,11 @@
       <c r="F11" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -6682,8 +7060,11 @@
       <c r="F12" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -6702,8 +7083,11 @@
       <c r="F13" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6722,8 +7106,11 @@
       <c r="F14" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -6742,8 +7129,11 @@
       <c r="F15" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -6762,8 +7152,11 @@
       <c r="F16" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -6782,8 +7175,11 @@
       <c r="F17" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -6802,8 +7198,11 @@
       <c r="F18" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -6822,8 +7221,11 @@
       <c r="F19" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -6842,8 +7244,11 @@
       <c r="F20" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -6861,6 +7266,9 @@
       </c>
       <c r="F21" t="s">
         <v>281</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -6874,7 +7282,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7334B831-10DC-4F15-AFA2-B9F3057ACD46}">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6885,7 +7293,7 @@
     <col min="6" max="6" width="61.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -6904,8 +7312,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6924,8 +7335,11 @@
       <c r="F2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6944,8 +7358,11 @@
       <c r="F3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6964,8 +7381,11 @@
       <c r="F4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6984,8 +7404,11 @@
       <c r="F5" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7004,8 +7427,11 @@
       <c r="F6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7024,8 +7450,11 @@
       <c r="F7" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7044,8 +7473,11 @@
       <c r="F8" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7064,8 +7496,11 @@
       <c r="F9" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7084,8 +7519,11 @@
       <c r="F10" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -7104,8 +7542,11 @@
       <c r="F11" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -7124,8 +7565,11 @@
       <c r="F12" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -7144,8 +7588,11 @@
       <c r="F13" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7164,8 +7611,11 @@
       <c r="F14" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -7184,8 +7634,11 @@
       <c r="F15" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -7204,8 +7657,11 @@
       <c r="F16" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -7224,8 +7680,11 @@
       <c r="F17" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -7244,8 +7703,11 @@
       <c r="F18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -7264,8 +7726,11 @@
       <c r="F19" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -7284,8 +7749,11 @@
       <c r="F20" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -7303,6 +7771,9 @@
       </c>
       <c r="F21" t="s">
         <v>356</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -7316,7 +7787,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCAD424-DE97-4AD0-8EC6-09AC549E06E2}">
   <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7327,7 +7798,7 @@
     <col min="6" max="6" width="66.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -7346,8 +7817,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7366,8 +7840,11 @@
       <c r="F2" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7386,8 +7863,11 @@
       <c r="F3" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7406,8 +7886,11 @@
       <c r="F4" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7426,8 +7909,11 @@
       <c r="F5" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7446,8 +7932,11 @@
       <c r="F6" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7466,8 +7955,11 @@
       <c r="F7" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7486,8 +7978,11 @@
       <c r="F8" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7506,8 +8001,11 @@
       <c r="F9" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7526,8 +8024,11 @@
       <c r="F10" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -7546,8 +8047,11 @@
       <c r="F11" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -7566,8 +8070,11 @@
       <c r="F12" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -7586,8 +8093,11 @@
       <c r="F13" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7606,8 +8116,11 @@
       <c r="F14" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -7626,8 +8139,11 @@
       <c r="F15" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +8162,11 @@
       <c r="F16" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -7666,8 +8185,11 @@
       <c r="F17" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -7686,8 +8208,11 @@
       <c r="F18" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -7706,8 +8231,11 @@
       <c r="F19" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -7726,8 +8254,11 @@
       <c r="F20" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -7745,6 +8276,9 @@
       </c>
       <c r="F21" t="s">
         <v>457</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -7758,7 +8292,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C645B9B6-6B08-49FC-A218-768498710ED2}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7769,7 +8303,7 @@
     <col min="6" max="6" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -7788,8 +8322,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7808,8 +8345,11 @@
       <c r="F2" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7828,8 +8368,11 @@
       <c r="F3" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7848,8 +8391,11 @@
       <c r="F4" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7868,8 +8414,11 @@
       <c r="F5" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7888,8 +8437,11 @@
       <c r="F6" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7908,8 +8460,11 @@
       <c r="F7" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7928,8 +8483,11 @@
       <c r="F8" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7948,8 +8506,11 @@
       <c r="F9" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7968,8 +8529,11 @@
       <c r="F10" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -7988,8 +8552,11 @@
       <c r="F11" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -8008,8 +8575,11 @@
       <c r="F12" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -8028,8 +8598,11 @@
       <c r="F13" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8048,8 +8621,11 @@
       <c r="F14" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -8068,8 +8644,11 @@
       <c r="F15" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -8088,8 +8667,11 @@
       <c r="F16" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -8108,8 +8690,11 @@
       <c r="F17" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -8128,8 +8713,11 @@
       <c r="F18" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -8148,8 +8736,11 @@
       <c r="F19" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -8168,8 +8759,11 @@
       <c r="F20" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -8187,6 +8781,9 @@
       </c>
       <c r="F21" t="s">
         <v>554</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -8200,7 +8797,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A32343-D22E-4277-935F-81201F7A6213}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8211,7 +8808,7 @@
     <col min="6" max="6" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -8230,8 +8827,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8250,8 +8850,11 @@
       <c r="F2" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8270,8 +8873,11 @@
       <c r="F3" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8290,8 +8896,11 @@
       <c r="F4" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -8310,8 +8919,11 @@
       <c r="F5" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -8330,8 +8942,11 @@
       <c r="F6" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8350,8 +8965,11 @@
       <c r="F7" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -8370,8 +8988,11 @@
       <c r="F8" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -8390,8 +9011,11 @@
       <c r="F9" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8410,8 +9034,11 @@
       <c r="F10" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -8430,8 +9057,11 @@
       <c r="F11" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -8450,8 +9080,11 @@
       <c r="F12" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -8470,8 +9103,11 @@
       <c r="F13" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8490,8 +9126,11 @@
       <c r="F14" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -8510,8 +9149,11 @@
       <c r="F15" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -8530,8 +9172,11 @@
       <c r="F16" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -8550,8 +9195,11 @@
       <c r="F17" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -8570,8 +9218,11 @@
       <c r="F18" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -8590,8 +9241,11 @@
       <c r="F19" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -8610,8 +9264,11 @@
       <c r="F20" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -8629,6 +9286,9 @@
       </c>
       <c r="F21" t="s">
         <v>641</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -8642,7 +9302,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224AAB98-BE98-4BAB-8261-8912BFC49626}">
   <sheetPr codeName="Sheet17"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8653,7 +9313,7 @@
     <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -8672,8 +9332,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8692,8 +9355,11 @@
       <c r="F2" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8712,8 +9378,11 @@
       <c r="F3" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8732,8 +9401,11 @@
       <c r="F4" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -8752,8 +9424,11 @@
       <c r="F5" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -8772,8 +9447,11 @@
       <c r="F6" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8792,8 +9470,11 @@
       <c r="F7" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -8812,8 +9493,11 @@
       <c r="F8" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -8832,8 +9516,11 @@
       <c r="F9" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8852,8 +9539,11 @@
       <c r="F10" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -8872,8 +9562,11 @@
       <c r="F11" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -8892,8 +9585,11 @@
       <c r="F12" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -8912,8 +9608,11 @@
       <c r="F13" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8932,8 +9631,11 @@
       <c r="F14" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -8952,8 +9654,11 @@
       <c r="F15" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -8972,8 +9677,11 @@
       <c r="F16" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -8992,8 +9700,11 @@
       <c r="F17" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -9012,8 +9723,11 @@
       <c r="F18" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -9032,8 +9746,11 @@
       <c r="F19" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -9052,8 +9769,11 @@
       <c r="F20" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -9071,6 +9791,9 @@
       </c>
       <c r="F21" t="s">
         <v>737</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -9084,7 +9807,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869F92E5-F899-4934-868C-23F77BED8C35}">
   <sheetPr codeName="Sheet16"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9094,7 +9817,7 @@
     <col min="6" max="6" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -9113,8 +9836,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9133,8 +9859,11 @@
       <c r="F2" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -9153,8 +9882,11 @@
       <c r="F3" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -9173,8 +9905,11 @@
       <c r="F4" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -9193,8 +9928,11 @@
       <c r="F5" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -9213,8 +9951,11 @@
       <c r="F6" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -9233,8 +9974,11 @@
       <c r="F7" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -9253,8 +9997,11 @@
       <c r="F8" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -9273,8 +10020,11 @@
       <c r="F9" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -9293,8 +10043,11 @@
       <c r="F10" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -9313,8 +10066,11 @@
       <c r="F11" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -9333,8 +10089,11 @@
       <c r="F12" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -9353,8 +10112,11 @@
       <c r="F13" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -9373,8 +10135,11 @@
       <c r="F14" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -9393,8 +10158,11 @@
       <c r="F15" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -9413,8 +10181,11 @@
       <c r="F16" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -9433,8 +10204,11 @@
       <c r="F17" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -9453,8 +10227,11 @@
       <c r="F18" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -9473,8 +10250,11 @@
       <c r="F19" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -9493,8 +10273,11 @@
       <c r="F20" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -9512,6 +10295,9 @@
       </c>
       <c r="F21" t="s">
         <v>830</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
